--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:36</t>
+    <t xml:space="preserve">2026-09-09 22:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:22</t>
+    <t xml:space="preserve">2026-09-12 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:39</t>
+    <t xml:space="preserve">2026-09-24 00:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:16</t>
+    <t xml:space="preserve">2026-09-27 22:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:06</t>
+    <t xml:space="preserve">2026-09-29 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,7 +517,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>15.93</v>
+        <v>159.26</v>
       </c>
     </row>
     <row r="3">
@@ -534,7 +534,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14.63</v>
+        <v>146.26</v>
       </c>
     </row>
     <row r="4">
@@ -551,7 +551,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12.79</v>
+        <v>127.85</v>
       </c>
     </row>
     <row r="5">
@@ -568,7 +568,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12.76</v>
+        <v>127.61</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12.31</v>
+        <v>123.09</v>
       </c>
     </row>
     <row r="7">
@@ -602,7 +602,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11.92</v>
+        <v>119.24</v>
       </c>
     </row>
     <row r="8">
@@ -619,7 +619,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11.52</v>
+        <v>115.18</v>
       </c>
     </row>
     <row r="9">
@@ -636,7 +636,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11.47</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="10">
@@ -653,7 +653,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11.27</v>
+        <v>112.72</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11.07</v>
+        <v>110.68</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +687,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9.21</v>
+        <v>92.1</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>9.08</v>
+        <v>90.78</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:00</t>
+    <t xml:space="preserve">2026-10-01 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:25</t>
+    <t xml:space="preserve">2026-10-02 13:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:14</t>
+    <t xml:space="preserve">2026-10-05 07:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
